--- a/rcads/data/xls/31_ResponseOptions.xlsx
+++ b/rcads/data/xls/31_ResponseOptions.xlsx
@@ -10,7 +10,7 @@
     <sheet sheetId="1" r:id="rId1" name="_31_ResponseOptions"/>
   </sheets>
   <definedNames>
-    <definedName name="_31_ResponseOptions">'_31_ResponseOptions'!$A$1:$D$167</definedName>
+    <definedName name="_31_ResponseOptions">'_31_ResponseOptions'!$A$1:$D$184</definedName>
   </definedNames>
   <calcPr calcId="125725" fullCalcOnLoad="true"/>
 </workbook>
@@ -343,7 +343,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D167"/>
+  <dimension ref="A1:D184"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row outlineLevel="0" r="1">
@@ -3025,6 +3025,278 @@
         </is>
       </c>
     </row>
+    <row outlineLevel="0" r="168">
+      <c r="A168" s="0">
+        <v>169</v>
+      </c>
+      <c r="B168" s="0">
+        <v>1</v>
+      </c>
+      <c r="C168" s="0">
+        <v>25</v>
+      </c>
+      <c r="D168" s="0" t="inlineStr">
+        <is>
+          <t>從來沒有</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="169">
+      <c r="A169" s="0">
+        <v>170</v>
+      </c>
+      <c r="B169" s="0">
+        <v>2</v>
+      </c>
+      <c r="C169" s="0">
+        <v>25</v>
+      </c>
+      <c r="D169" s="0" t="inlineStr">
+        <is>
+          <t>間中這樣</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="170">
+      <c r="A170" s="0">
+        <v>171</v>
+      </c>
+      <c r="B170" s="0">
+        <v>3</v>
+      </c>
+      <c r="C170" s="0">
+        <v>25</v>
+      </c>
+      <c r="D170" s="0" t="inlineStr">
+        <is>
+          <t>很多時這樣</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="171">
+      <c r="A171" s="0">
+        <v>172</v>
+      </c>
+      <c r="B171" s="0">
+        <v>4</v>
+      </c>
+      <c r="C171" s="0">
+        <v>25</v>
+      </c>
+      <c r="D171" s="0" t="inlineStr">
+        <is>
+          <t>經常這樣</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="172">
+      <c r="A172" s="0">
+        <v>173</v>
+      </c>
+      <c r="B172" s="0">
+        <v>1</v>
+      </c>
+      <c r="C172" s="0">
+        <v>28</v>
+      </c>
+      <c r="D172" s="0" t="inlineStr">
+        <is>
+          <t>Tidak pernah</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="173">
+      <c r="A173" s="0">
+        <v>174</v>
+      </c>
+      <c r="B173" s="0">
+        <v>2</v>
+      </c>
+      <c r="C173" s="0">
+        <v>28</v>
+      </c>
+      <c r="D173" s="0" t="inlineStr">
+        <is>
+          <t>Kadang-kadang</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="174">
+      <c r="A174" s="0">
+        <v>175</v>
+      </c>
+      <c r="B174" s="0">
+        <v>3</v>
+      </c>
+      <c r="C174" s="0">
+        <v>28</v>
+      </c>
+      <c r="D174" s="0" t="inlineStr">
+        <is>
+          <t>Kerap</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="175">
+      <c r="A175" s="0">
+        <v>176</v>
+      </c>
+      <c r="B175" s="0">
+        <v>4</v>
+      </c>
+      <c r="C175" s="0">
+        <v>28</v>
+      </c>
+      <c r="D175" s="0" t="inlineStr">
+        <is>
+          <t>Selalu</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="176">
+      <c r="A176" s="0">
+        <v>177</v>
+      </c>
+      <c r="B176" s="0">
+        <v>1</v>
+      </c>
+      <c r="C176" s="0">
+        <v>42</v>
+      </c>
+      <c r="D176" s="0" t="inlineStr">
+        <is>
+          <t>Asnjëherë</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="177">
+      <c r="A177" s="0">
+        <v>178</v>
+      </c>
+      <c r="B177" s="0">
+        <v>2</v>
+      </c>
+      <c r="C177" s="0">
+        <v>42</v>
+      </c>
+      <c r="D177" s="0" t="inlineStr">
+        <is>
+          <t>Ndonjëherë</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="178">
+      <c r="A178" s="0">
+        <v>179</v>
+      </c>
+      <c r="B178" s="0">
+        <v>3</v>
+      </c>
+      <c r="C178" s="0">
+        <v>42</v>
+      </c>
+      <c r="D178" s="0" t="inlineStr">
+        <is>
+          <t>Shpesh</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="179">
+      <c r="A179" s="0">
+        <v>180</v>
+      </c>
+      <c r="B179" s="0">
+        <v>4</v>
+      </c>
+      <c r="C179" s="0">
+        <v>42</v>
+      </c>
+      <c r="D179" s="0" t="inlineStr">
+        <is>
+          <t>Gjithmonë</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="180">
+      <c r="A180" s="0">
+        <v>181</v>
+      </c>
+      <c r="B180" s="0">
+        <v>11</v>
+      </c>
+      <c r="C180" s="0">
+        <v>1</v>
+      </c>
+      <c r="D180" s="0" t="inlineStr">
+        <is>
+          <t>More than half of the two week period</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="181">
+      <c r="A181" s="0">
+        <v>182</v>
+      </c>
+      <c r="B181" s="0">
+        <v>9</v>
+      </c>
+      <c r="C181" s="0">
+        <v>8</v>
+      </c>
+      <c r="D181" s="0" t="inlineStr">
+        <is>
+          <t>Jamais</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="182">
+      <c r="A182" s="0">
+        <v>183</v>
+      </c>
+      <c r="B182" s="0">
+        <v>10</v>
+      </c>
+      <c r="C182" s="0">
+        <v>8</v>
+      </c>
+      <c r="D182" s="0" t="inlineStr">
+        <is>
+          <t>Plusieurs jours</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="183">
+      <c r="A183" s="0">
+        <v>184</v>
+      </c>
+      <c r="B183" s="0">
+        <v>11</v>
+      </c>
+      <c r="C183" s="0">
+        <v>8</v>
+      </c>
+      <c r="D183" s="0" t="inlineStr">
+        <is>
+          <t>Plus de la moitié du temps</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="184">
+      <c r="A184" s="0">
+        <v>185</v>
+      </c>
+      <c r="B184" s="0">
+        <v>12</v>
+      </c>
+      <c r="C184" s="0">
+        <v>8</v>
+      </c>
+      <c r="D184" s="0" t="inlineStr">
+        <is>
+          <t>Presque tous les jours</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
